--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -869,59 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132853335</v>
+        <v>132849625</v>
       </c>
       <c r="B4" t="n">
-        <v>93206</v>
+        <v>79365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439146</v>
+        <v>439587</v>
       </c>
       <c r="R4" t="n">
-        <v>6883811</v>
+        <v>6883256</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -980,45 +966,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132853049</v>
+        <v>132853335</v>
       </c>
       <c r="B5" t="n">
-        <v>79412</v>
+        <v>93206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439230</v>
+        <v>439146</v>
       </c>
       <c r="R5" t="n">
-        <v>6883797</v>
+        <v>6883811</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132849625</v>
+        <v>132853049</v>
       </c>
       <c r="B6" t="n">
-        <v>79365</v>
+        <v>79412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,21 +1088,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439587</v>
+        <v>439230</v>
       </c>
       <c r="R6" t="n">
-        <v>6883256</v>
+        <v>6883797</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132854581</v>
+        <v>132855316</v>
       </c>
       <c r="B15" t="n">
-        <v>79952</v>
+        <v>92518</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439075</v>
+        <v>439197</v>
       </c>
       <c r="R15" t="n">
-        <v>6883547</v>
+        <v>6883484</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132854672</v>
+        <v>132854581</v>
       </c>
       <c r="B16" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439113</v>
+        <v>439075</v>
       </c>
       <c r="R16" t="n">
-        <v>6883492</v>
+        <v>6883547</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2154,32 +2154,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132855316</v>
+        <v>132854672</v>
       </c>
       <c r="B17" t="n">
-        <v>92518</v>
+        <v>79091</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439197</v>
+        <v>439113</v>
       </c>
       <c r="R17" t="n">
-        <v>6883484</v>
+        <v>6883492</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2251,32 +2251,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132856227</v>
+        <v>132849808</v>
       </c>
       <c r="B18" t="n">
-        <v>98001</v>
+        <v>79365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439643</v>
+        <v>439579</v>
       </c>
       <c r="R18" t="n">
-        <v>6883340</v>
+        <v>6883290</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132849808</v>
+        <v>132856227</v>
       </c>
       <c r="B21" t="n">
-        <v>79365</v>
+        <v>98001</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439579</v>
+        <v>439643</v>
       </c>
       <c r="R21" t="n">
-        <v>6883290</v>
+        <v>6883340</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2639,10 +2639,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132856307</v>
+        <v>132849022</v>
       </c>
       <c r="B22" t="n">
-        <v>79412</v>
+        <v>79365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,21 +2650,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439692</v>
+        <v>439502</v>
       </c>
       <c r="R22" t="n">
-        <v>6883295</v>
+        <v>6883177</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,32 +2736,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132853019</v>
+        <v>132853397</v>
       </c>
       <c r="B23" t="n">
-        <v>80467</v>
+        <v>79091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439235</v>
+        <v>439117</v>
       </c>
       <c r="R23" t="n">
-        <v>6883808</v>
+        <v>6883809</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132853397</v>
+        <v>132856307</v>
       </c>
       <c r="B24" t="n">
-        <v>79091</v>
+        <v>79412</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439117</v>
+        <v>439692</v>
       </c>
       <c r="R24" t="n">
-        <v>6883809</v>
+        <v>6883295</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132849022</v>
+        <v>132853019</v>
       </c>
       <c r="B25" t="n">
-        <v>79365</v>
+        <v>80467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439502</v>
+        <v>439235</v>
       </c>
       <c r="R25" t="n">
-        <v>6883177</v>
+        <v>6883808</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132852187</v>
+        <v>132852127</v>
       </c>
       <c r="B29" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3329,21 +3329,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439386</v>
+        <v>439412</v>
       </c>
       <c r="R29" t="n">
-        <v>6883624</v>
+        <v>6883600</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3415,7 +3415,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132856616</v>
+        <v>132852187</v>
       </c>
       <c r="B30" t="n">
         <v>80439</v>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439678</v>
+        <v>439386</v>
       </c>
       <c r="R30" t="n">
-        <v>6883172</v>
+        <v>6883624</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132852127</v>
+        <v>132850734</v>
       </c>
       <c r="B31" t="n">
         <v>79412</v>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439412</v>
+        <v>439680</v>
       </c>
       <c r="R31" t="n">
-        <v>6883600</v>
+        <v>6883392</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3583,6 +3583,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3609,10 +3614,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132850734</v>
+        <v>132856616</v>
       </c>
       <c r="B32" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3620,21 +3625,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3644,10 +3649,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439680</v>
+        <v>439678</v>
       </c>
       <c r="R32" t="n">
-        <v>6883392</v>
+        <v>6883172</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3680,11 +3685,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132853499</v>
+        <v>132849181</v>
       </c>
       <c r="B38" t="n">
-        <v>79412</v>
+        <v>79090</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439076</v>
+        <v>439494</v>
       </c>
       <c r="R38" t="n">
-        <v>6883736</v>
+        <v>6883219</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4303,7 +4303,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132852930</v>
+        <v>132853499</v>
       </c>
       <c r="B39" t="n">
         <v>79412</v>
@@ -4338,13 +4338,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439247</v>
+        <v>439076</v>
       </c>
       <c r="R39" t="n">
-        <v>6883824</v>
+        <v>6883736</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4374,11 +4374,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4405,10 +4400,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132853884</v>
+        <v>132852930</v>
       </c>
       <c r="B40" t="n">
-        <v>79365</v>
+        <v>79412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4416,21 +4411,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4440,13 +4435,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439130</v>
+        <v>439247</v>
       </c>
       <c r="R40" t="n">
-        <v>6883643</v>
+        <v>6883824</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4476,6 +4471,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4502,10 +4502,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132849181</v>
+        <v>132853884</v>
       </c>
       <c r="B41" t="n">
-        <v>79090</v>
+        <v>79365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4513,21 +4513,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439494</v>
+        <v>439130</v>
       </c>
       <c r="R41" t="n">
-        <v>6883219</v>
+        <v>6883643</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4599,10 +4599,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132851872</v>
+        <v>132851614</v>
       </c>
       <c r="B42" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4610,21 +4610,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439529</v>
+        <v>439614</v>
       </c>
       <c r="R42" t="n">
-        <v>6883531</v>
+        <v>6883457</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132851614</v>
+        <v>132851872</v>
       </c>
       <c r="B43" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4707,21 +4707,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439614</v>
+        <v>439529</v>
       </c>
       <c r="R43" t="n">
-        <v>6883457</v>
+        <v>6883531</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5181,10 +5181,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132849550</v>
+        <v>132849417</v>
       </c>
       <c r="B48" t="n">
-        <v>79412</v>
+        <v>79952</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5192,21 +5192,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439556</v>
+        <v>439558</v>
       </c>
       <c r="R48" t="n">
-        <v>6883244</v>
+        <v>6883256</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132849417</v>
+        <v>132849550</v>
       </c>
       <c r="B49" t="n">
-        <v>79952</v>
+        <v>79412</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5289,21 +5289,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439558</v>
+        <v>439556</v>
       </c>
       <c r="R49" t="n">
-        <v>6883256</v>
+        <v>6883244</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132853541</v>
+        <v>132851662</v>
       </c>
       <c r="B2" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439124</v>
+        <v>439581</v>
       </c>
       <c r="R2" t="n">
-        <v>6883715</v>
+        <v>6883476</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132851662</v>
+        <v>132853541</v>
       </c>
       <c r="B3" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439581</v>
+        <v>439124</v>
       </c>
       <c r="R3" t="n">
-        <v>6883476</v>
+        <v>6883715</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132849625</v>
+        <v>132853049</v>
       </c>
       <c r="B4" t="n">
-        <v>79365</v>
+        <v>79412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439587</v>
+        <v>439230</v>
       </c>
       <c r="R4" t="n">
-        <v>6883256</v>
+        <v>6883797</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132853049</v>
+        <v>132849625</v>
       </c>
       <c r="B6" t="n">
-        <v>79412</v>
+        <v>79365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,21 +1088,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439230</v>
+        <v>439587</v>
       </c>
       <c r="R6" t="n">
-        <v>6883797</v>
+        <v>6883256</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132851109</v>
+        <v>132852859</v>
       </c>
       <c r="B13" t="n">
-        <v>79412</v>
+        <v>57145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439620</v>
+        <v>439262</v>
       </c>
       <c r="R13" t="n">
-        <v>6883420</v>
+        <v>6883822</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1832,6 +1832,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132852859</v>
+        <v>132851109</v>
       </c>
       <c r="B14" t="n">
-        <v>57145</v>
+        <v>79412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439262</v>
+        <v>439620</v>
       </c>
       <c r="R14" t="n">
-        <v>6883822</v>
+        <v>6883420</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1929,11 +1934,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132855316</v>
+        <v>132854672</v>
       </c>
       <c r="B15" t="n">
-        <v>92518</v>
+        <v>79091</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439197</v>
+        <v>439113</v>
       </c>
       <c r="R15" t="n">
-        <v>6883484</v>
+        <v>6883492</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2057,32 +2057,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132854581</v>
+        <v>132855316</v>
       </c>
       <c r="B16" t="n">
-        <v>79952</v>
+        <v>92518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>760</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439075</v>
+        <v>439197</v>
       </c>
       <c r="R16" t="n">
-        <v>6883547</v>
+        <v>6883484</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132854672</v>
+        <v>132854581</v>
       </c>
       <c r="B17" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,21 +2165,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439113</v>
+        <v>439075</v>
       </c>
       <c r="R17" t="n">
-        <v>6883492</v>
+        <v>6883547</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132849808</v>
+        <v>132855166</v>
       </c>
       <c r="B18" t="n">
-        <v>79365</v>
+        <v>80439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,21 +2262,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439579</v>
+        <v>439162</v>
       </c>
       <c r="R18" t="n">
-        <v>6883290</v>
+        <v>6883543</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2445,32 +2445,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132855166</v>
+        <v>132856227</v>
       </c>
       <c r="B20" t="n">
-        <v>80439</v>
+        <v>98001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439162</v>
+        <v>439643</v>
       </c>
       <c r="R20" t="n">
-        <v>6883543</v>
+        <v>6883340</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132856227</v>
+        <v>132849808</v>
       </c>
       <c r="B21" t="n">
-        <v>98001</v>
+        <v>79365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439643</v>
+        <v>439579</v>
       </c>
       <c r="R21" t="n">
-        <v>6883340</v>
+        <v>6883290</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132853955</v>
+        <v>132852127</v>
       </c>
       <c r="B28" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439099</v>
+        <v>439412</v>
       </c>
       <c r="R28" t="n">
-        <v>6883602</v>
+        <v>6883600</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132852127</v>
+        <v>132850734</v>
       </c>
       <c r="B29" t="n">
         <v>79412</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439412</v>
+        <v>439680</v>
       </c>
       <c r="R29" t="n">
-        <v>6883600</v>
+        <v>6883392</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3389,6 +3389,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3415,10 +3420,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132852187</v>
+        <v>132851377</v>
       </c>
       <c r="B30" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3426,21 +3431,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3450,10 +3455,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439386</v>
+        <v>439619</v>
       </c>
       <c r="R30" t="n">
-        <v>6883624</v>
+        <v>6883455</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3486,6 +3491,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3512,7 +3522,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132850734</v>
+        <v>132852517</v>
       </c>
       <c r="B31" t="n">
         <v>79412</v>
@@ -3547,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439680</v>
+        <v>439354</v>
       </c>
       <c r="R31" t="n">
-        <v>6883392</v>
+        <v>6883624</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3583,11 +3593,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3614,7 +3619,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132856616</v>
+        <v>132853955</v>
       </c>
       <c r="B32" t="n">
         <v>80439</v>
@@ -3649,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439678</v>
+        <v>439099</v>
       </c>
       <c r="R32" t="n">
-        <v>6883172</v>
+        <v>6883602</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3711,10 +3716,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132851377</v>
+        <v>132852187</v>
       </c>
       <c r="B33" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3722,21 +3727,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3746,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439619</v>
+        <v>439386</v>
       </c>
       <c r="R33" t="n">
-        <v>6883455</v>
+        <v>6883624</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3782,11 +3787,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3813,10 +3813,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132852517</v>
+        <v>132856616</v>
       </c>
       <c r="B34" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3824,21 +3824,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439354</v>
+        <v>439678</v>
       </c>
       <c r="R34" t="n">
-        <v>6883624</v>
+        <v>6883172</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132852715</v>
+        <v>132851426</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>79412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439316</v>
+        <v>439631</v>
       </c>
       <c r="R35" t="n">
-        <v>6883738</v>
+        <v>6883466</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -3981,6 +3981,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4007,10 +4012,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132851426</v>
+        <v>132852715</v>
       </c>
       <c r="B36" t="n">
-        <v>79412</v>
+        <v>79333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4018,21 +4023,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4042,10 +4047,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439631</v>
+        <v>439316</v>
       </c>
       <c r="R36" t="n">
-        <v>6883466</v>
+        <v>6883738</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4078,11 +4083,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5181,10 +5181,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132849417</v>
+        <v>132849550</v>
       </c>
       <c r="B48" t="n">
-        <v>79952</v>
+        <v>79412</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5192,21 +5192,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439558</v>
+        <v>439556</v>
       </c>
       <c r="R48" t="n">
-        <v>6883256</v>
+        <v>6883244</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132849550</v>
+        <v>132849417</v>
       </c>
       <c r="B49" t="n">
-        <v>79412</v>
+        <v>79952</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5289,21 +5289,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439556</v>
+        <v>439558</v>
       </c>
       <c r="R49" t="n">
-        <v>6883244</v>
+        <v>6883256</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5375,32 +5375,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132852000</v>
+        <v>132849144</v>
       </c>
       <c r="B50" t="n">
-        <v>57145</v>
+        <v>79090</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5410,13 +5410,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439419</v>
+        <v>439508</v>
       </c>
       <c r="R50" t="n">
-        <v>6883604</v>
+        <v>6883212</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5446,11 +5446,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5477,32 +5472,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132849144</v>
+        <v>132852000</v>
       </c>
       <c r="B51" t="n">
-        <v>79090</v>
+        <v>57145</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5512,13 +5507,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>439508</v>
+        <v>439419</v>
       </c>
       <c r="R51" t="n">
-        <v>6883212</v>
+        <v>6883604</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5548,6 +5543,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132851662</v>
+        <v>132853541</v>
       </c>
       <c r="B2" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439581</v>
+        <v>439124</v>
       </c>
       <c r="R2" t="n">
-        <v>6883476</v>
+        <v>6883715</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132853541</v>
+        <v>132851662</v>
       </c>
       <c r="B3" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439124</v>
+        <v>439581</v>
       </c>
       <c r="R3" t="n">
-        <v>6883715</v>
+        <v>6883476</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132851231</v>
+        <v>132852203</v>
       </c>
       <c r="B7" t="n">
-        <v>79412</v>
+        <v>79923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439625</v>
+        <v>439393</v>
       </c>
       <c r="R7" t="n">
-        <v>6883432</v>
+        <v>6883615</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1271,32 +1271,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132852732</v>
+        <v>132851231</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>79412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439310</v>
+        <v>439625</v>
       </c>
       <c r="R8" t="n">
-        <v>6883738</v>
+        <v>6883432</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1342,11 +1342,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,32 +1368,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132852203</v>
+        <v>132852732</v>
       </c>
       <c r="B9" t="n">
-        <v>79923</v>
+        <v>57145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439393</v>
+        <v>439310</v>
       </c>
       <c r="R9" t="n">
-        <v>6883615</v>
+        <v>6883738</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1444,6 +1439,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132852859</v>
+        <v>132851109</v>
       </c>
       <c r="B13" t="n">
-        <v>57145</v>
+        <v>79412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439262</v>
+        <v>439620</v>
       </c>
       <c r="R13" t="n">
-        <v>6883822</v>
+        <v>6883420</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1832,11 +1832,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1863,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132851109</v>
+        <v>132852859</v>
       </c>
       <c r="B14" t="n">
-        <v>79412</v>
+        <v>57145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439620</v>
+        <v>439262</v>
       </c>
       <c r="R14" t="n">
-        <v>6883420</v>
+        <v>6883822</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1934,6 +1929,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1960,10 +1960,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132854672</v>
+        <v>132854581</v>
       </c>
       <c r="B15" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,21 +1971,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439113</v>
+        <v>439075</v>
       </c>
       <c r="R15" t="n">
-        <v>6883492</v>
+        <v>6883547</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132854581</v>
+        <v>132854672</v>
       </c>
       <c r="B17" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,21 +2165,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439075</v>
+        <v>439113</v>
       </c>
       <c r="R17" t="n">
-        <v>6883547</v>
+        <v>6883492</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132851342</v>
+        <v>132849808</v>
       </c>
       <c r="B19" t="n">
-        <v>79090</v>
+        <v>79365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439612</v>
+        <v>439579</v>
       </c>
       <c r="R19" t="n">
-        <v>6883462</v>
+        <v>6883290</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2445,32 +2445,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132856227</v>
+        <v>132851342</v>
       </c>
       <c r="B20" t="n">
-        <v>98001</v>
+        <v>79090</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439643</v>
+        <v>439612</v>
       </c>
       <c r="R20" t="n">
-        <v>6883340</v>
+        <v>6883462</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132849808</v>
+        <v>132856227</v>
       </c>
       <c r="B21" t="n">
-        <v>79365</v>
+        <v>98001</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439579</v>
+        <v>439643</v>
       </c>
       <c r="R21" t="n">
-        <v>6883290</v>
+        <v>6883340</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2639,10 +2639,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132849022</v>
+        <v>132853397</v>
       </c>
       <c r="B22" t="n">
-        <v>79365</v>
+        <v>79091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,21 +2650,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439502</v>
+        <v>439117</v>
       </c>
       <c r="R22" t="n">
-        <v>6883177</v>
+        <v>6883809</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132853397</v>
+        <v>132849022</v>
       </c>
       <c r="B23" t="n">
-        <v>79091</v>
+        <v>79365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439117</v>
+        <v>439502</v>
       </c>
       <c r="R23" t="n">
-        <v>6883809</v>
+        <v>6883177</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132856307</v>
+        <v>132853019</v>
       </c>
       <c r="B24" t="n">
-        <v>79412</v>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439692</v>
+        <v>439235</v>
       </c>
       <c r="R24" t="n">
-        <v>6883295</v>
+        <v>6883808</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,32 +2930,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132853019</v>
+        <v>132856307</v>
       </c>
       <c r="B25" t="n">
-        <v>80467</v>
+        <v>79412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439235</v>
+        <v>439692</v>
       </c>
       <c r="R25" t="n">
-        <v>6883808</v>
+        <v>6883295</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132852127</v>
+        <v>132853955</v>
       </c>
       <c r="B28" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439412</v>
+        <v>439099</v>
       </c>
       <c r="R28" t="n">
-        <v>6883600</v>
+        <v>6883602</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132850734</v>
+        <v>132852127</v>
       </c>
       <c r="B29" t="n">
         <v>79412</v>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439680</v>
+        <v>439412</v>
       </c>
       <c r="R29" t="n">
-        <v>6883392</v>
+        <v>6883600</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3389,11 +3389,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3420,10 +3415,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132851377</v>
+        <v>132852187</v>
       </c>
       <c r="B30" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3431,21 +3426,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3455,10 +3450,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439619</v>
+        <v>439386</v>
       </c>
       <c r="R30" t="n">
-        <v>6883455</v>
+        <v>6883624</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3491,11 +3486,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3522,7 +3512,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132852517</v>
+        <v>132850734</v>
       </c>
       <c r="B31" t="n">
         <v>79412</v>
@@ -3557,10 +3547,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439354</v>
+        <v>439680</v>
       </c>
       <c r="R31" t="n">
-        <v>6883624</v>
+        <v>6883392</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3593,6 +3583,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3619,7 +3614,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132853955</v>
+        <v>132856616</v>
       </c>
       <c r="B32" t="n">
         <v>80439</v>
@@ -3654,10 +3649,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439099</v>
+        <v>439678</v>
       </c>
       <c r="R32" t="n">
-        <v>6883602</v>
+        <v>6883172</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3716,10 +3711,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132852187</v>
+        <v>132851377</v>
       </c>
       <c r="B33" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3727,21 +3722,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3751,10 +3746,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439386</v>
+        <v>439619</v>
       </c>
       <c r="R33" t="n">
-        <v>6883624</v>
+        <v>6883455</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3787,6 +3782,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3813,10 +3813,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132856616</v>
+        <v>132852517</v>
       </c>
       <c r="B34" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3824,21 +3824,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439678</v>
+        <v>439354</v>
       </c>
       <c r="R34" t="n">
-        <v>6883172</v>
+        <v>6883624</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132851426</v>
+        <v>132848943</v>
       </c>
       <c r="B35" t="n">
-        <v>79412</v>
+        <v>80438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439631</v>
+        <v>439491</v>
       </c>
       <c r="R35" t="n">
-        <v>6883466</v>
+        <v>6883182</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -3981,11 +3981,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4109,10 +4104,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132848943</v>
+        <v>132851426</v>
       </c>
       <c r="B37" t="n">
-        <v>80438</v>
+        <v>79412</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,21 +4115,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4144,10 +4139,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439491</v>
+        <v>439631</v>
       </c>
       <c r="R37" t="n">
-        <v>6883182</v>
+        <v>6883466</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4180,6 +4175,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5084,10 +5084,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132852323</v>
+        <v>132849550</v>
       </c>
       <c r="B47" t="n">
-        <v>79952</v>
+        <v>79412</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5095,21 +5095,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439383</v>
+        <v>439556</v>
       </c>
       <c r="R47" t="n">
-        <v>6883628</v>
+        <v>6883244</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5181,10 +5181,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132849550</v>
+        <v>132849417</v>
       </c>
       <c r="B48" t="n">
-        <v>79412</v>
+        <v>79952</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5192,21 +5192,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439556</v>
+        <v>439558</v>
       </c>
       <c r="R48" t="n">
-        <v>6883244</v>
+        <v>6883256</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132849417</v>
+        <v>132852323</v>
       </c>
       <c r="B49" t="n">
         <v>79952</v>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439558</v>
+        <v>439383</v>
       </c>
       <c r="R49" t="n">
-        <v>6883256</v>
+        <v>6883628</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -869,45 +869,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132853049</v>
+        <v>132853335</v>
       </c>
       <c r="B4" t="n">
-        <v>79412</v>
+        <v>93206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439230</v>
+        <v>439146</v>
       </c>
       <c r="R4" t="n">
-        <v>6883797</v>
+        <v>6883811</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,59 +980,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132853335</v>
+        <v>132853049</v>
       </c>
       <c r="B5" t="n">
-        <v>93206</v>
+        <v>79412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439146</v>
+        <v>439230</v>
       </c>
       <c r="R5" t="n">
-        <v>6883811</v>
+        <v>6883797</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132852203</v>
+        <v>132851231</v>
       </c>
       <c r="B7" t="n">
-        <v>79923</v>
+        <v>79412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439393</v>
+        <v>439625</v>
       </c>
       <c r="R7" t="n">
-        <v>6883615</v>
+        <v>6883432</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1271,32 +1271,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132851231</v>
+        <v>132852732</v>
       </c>
       <c r="B8" t="n">
-        <v>79412</v>
+        <v>57145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439625</v>
+        <v>439310</v>
       </c>
       <c r="R8" t="n">
-        <v>6883432</v>
+        <v>6883738</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1342,6 +1342,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1368,32 +1373,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132852732</v>
+        <v>132852203</v>
       </c>
       <c r="B9" t="n">
-        <v>57145</v>
+        <v>79923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439310</v>
+        <v>439393</v>
       </c>
       <c r="R9" t="n">
-        <v>6883738</v>
+        <v>6883615</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1439,11 +1444,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1960,10 +1960,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132854581</v>
+        <v>132854672</v>
       </c>
       <c r="B15" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,21 +1971,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439075</v>
+        <v>439113</v>
       </c>
       <c r="R15" t="n">
-        <v>6883547</v>
+        <v>6883492</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132854672</v>
+        <v>132854581</v>
       </c>
       <c r="B17" t="n">
-        <v>79091</v>
+        <v>79952</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,21 +2165,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439113</v>
+        <v>439075</v>
       </c>
       <c r="R17" t="n">
-        <v>6883492</v>
+        <v>6883547</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132855166</v>
+        <v>132849808</v>
       </c>
       <c r="B18" t="n">
-        <v>80439</v>
+        <v>79365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,21 +2262,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439162</v>
+        <v>439579</v>
       </c>
       <c r="R18" t="n">
-        <v>6883543</v>
+        <v>6883290</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132849808</v>
+        <v>132855166</v>
       </c>
       <c r="B19" t="n">
-        <v>79365</v>
+        <v>80439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439579</v>
+        <v>439162</v>
       </c>
       <c r="R19" t="n">
-        <v>6883290</v>
+        <v>6883543</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2639,10 +2639,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132853397</v>
+        <v>132856307</v>
       </c>
       <c r="B22" t="n">
-        <v>79091</v>
+        <v>79412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,21 +2650,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439117</v>
+        <v>439692</v>
       </c>
       <c r="R22" t="n">
-        <v>6883809</v>
+        <v>6883295</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,32 +2736,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132849022</v>
+        <v>132853019</v>
       </c>
       <c r="B23" t="n">
-        <v>79365</v>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439502</v>
+        <v>439235</v>
       </c>
       <c r="R23" t="n">
-        <v>6883177</v>
+        <v>6883808</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132853019</v>
+        <v>132853397</v>
       </c>
       <c r="B24" t="n">
-        <v>80467</v>
+        <v>79091</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439235</v>
+        <v>439117</v>
       </c>
       <c r="R24" t="n">
-        <v>6883808</v>
+        <v>6883809</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132856307</v>
+        <v>132849022</v>
       </c>
       <c r="B25" t="n">
-        <v>79412</v>
+        <v>79365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439692</v>
+        <v>439502</v>
       </c>
       <c r="R25" t="n">
-        <v>6883295</v>
+        <v>6883177</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132848943</v>
+        <v>132852715</v>
       </c>
       <c r="B35" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439491</v>
+        <v>439316</v>
       </c>
       <c r="R35" t="n">
-        <v>6883182</v>
+        <v>6883738</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132852715</v>
+        <v>132851426</v>
       </c>
       <c r="B36" t="n">
-        <v>79333</v>
+        <v>79412</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439316</v>
+        <v>439631</v>
       </c>
       <c r="R36" t="n">
-        <v>6883738</v>
+        <v>6883466</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4078,6 +4078,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4104,10 +4109,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132851426</v>
+        <v>132848943</v>
       </c>
       <c r="B37" t="n">
-        <v>79412</v>
+        <v>80438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4115,21 +4120,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4139,10 +4144,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439631</v>
+        <v>439491</v>
       </c>
       <c r="R37" t="n">
-        <v>6883466</v>
+        <v>6883182</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4175,11 +4180,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132849181</v>
+        <v>132853499</v>
       </c>
       <c r="B38" t="n">
-        <v>79090</v>
+        <v>79412</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439494</v>
+        <v>439076</v>
       </c>
       <c r="R38" t="n">
-        <v>6883219</v>
+        <v>6883736</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4303,7 +4303,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132853499</v>
+        <v>132852930</v>
       </c>
       <c r="B39" t="n">
         <v>79412</v>
@@ -4338,13 +4338,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439076</v>
+        <v>439247</v>
       </c>
       <c r="R39" t="n">
-        <v>6883736</v>
+        <v>6883824</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4374,6 +4374,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4400,10 +4405,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132852930</v>
+        <v>132853884</v>
       </c>
       <c r="B40" t="n">
-        <v>79412</v>
+        <v>79365</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4411,21 +4416,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4435,13 +4440,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439247</v>
+        <v>439130</v>
       </c>
       <c r="R40" t="n">
-        <v>6883824</v>
+        <v>6883643</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4471,11 +4476,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4502,10 +4502,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132853884</v>
+        <v>132849181</v>
       </c>
       <c r="B41" t="n">
-        <v>79365</v>
+        <v>79090</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4513,21 +4513,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439130</v>
+        <v>439494</v>
       </c>
       <c r="R41" t="n">
-        <v>6883643</v>
+        <v>6883219</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132849316</v>
+        <v>132847930</v>
       </c>
       <c r="B44" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4804,21 +4804,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4828,13 +4828,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439497</v>
+        <v>439521</v>
       </c>
       <c r="R44" t="n">
-        <v>6883243</v>
+        <v>6883085</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132847930</v>
+        <v>132849316</v>
       </c>
       <c r="B46" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4998,21 +4998,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439521</v>
+        <v>439497</v>
       </c>
       <c r="R46" t="n">
-        <v>6883085</v>
+        <v>6883243</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5084,10 +5084,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132849550</v>
+        <v>132849417</v>
       </c>
       <c r="B47" t="n">
-        <v>79412</v>
+        <v>79952</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5095,21 +5095,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439556</v>
+        <v>439558</v>
       </c>
       <c r="R47" t="n">
-        <v>6883244</v>
+        <v>6883256</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5181,10 +5181,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132849417</v>
+        <v>132849550</v>
       </c>
       <c r="B48" t="n">
-        <v>79952</v>
+        <v>79412</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5192,21 +5192,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439558</v>
+        <v>439556</v>
       </c>
       <c r="R48" t="n">
-        <v>6883256</v>
+        <v>6883244</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5375,32 +5375,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132849144</v>
+        <v>132852000</v>
       </c>
       <c r="B50" t="n">
-        <v>79090</v>
+        <v>57145</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5410,13 +5410,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439508</v>
+        <v>439419</v>
       </c>
       <c r="R50" t="n">
-        <v>6883212</v>
+        <v>6883604</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5446,6 +5446,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5472,32 +5477,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132852000</v>
+        <v>132849144</v>
       </c>
       <c r="B51" t="n">
-        <v>57145</v>
+        <v>79090</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5507,13 +5512,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>439419</v>
+        <v>439508</v>
       </c>
       <c r="R51" t="n">
-        <v>6883604</v>
+        <v>6883212</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5543,11 +5548,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132851780</v>
+        <v>132852859</v>
       </c>
       <c r="B12" t="n">
-        <v>80439</v>
+        <v>57145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439589</v>
+        <v>439262</v>
       </c>
       <c r="R12" t="n">
-        <v>6883504</v>
+        <v>6883822</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1735,6 +1735,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,10 +1766,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132851109</v>
+        <v>132851780</v>
       </c>
       <c r="B13" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,21 +1777,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439620</v>
+        <v>439589</v>
       </c>
       <c r="R13" t="n">
-        <v>6883420</v>
+        <v>6883504</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1858,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132852859</v>
+        <v>132851109</v>
       </c>
       <c r="B14" t="n">
-        <v>57145</v>
+        <v>79412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439262</v>
+        <v>439620</v>
       </c>
       <c r="R14" t="n">
-        <v>6883822</v>
+        <v>6883420</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1929,11 +1934,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4890,7 +4890,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132848015</v>
+        <v>132849316</v>
       </c>
       <c r="B45" t="n">
         <v>79412</v>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439534</v>
+        <v>439497</v>
       </c>
       <c r="R45" t="n">
-        <v>6883074</v>
+        <v>6883243</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -4987,7 +4987,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132849316</v>
+        <v>132848015</v>
       </c>
       <c r="B46" t="n">
         <v>79412</v>
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439497</v>
+        <v>439534</v>
       </c>
       <c r="R46" t="n">
-        <v>6883243</v>
+        <v>6883074</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5084,7 +5084,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132849417</v>
+        <v>132852323</v>
       </c>
       <c r="B47" t="n">
         <v>79952</v>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439558</v>
+        <v>439383</v>
       </c>
       <c r="R47" t="n">
-        <v>6883256</v>
+        <v>6883628</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5181,10 +5181,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132849550</v>
+        <v>132849417</v>
       </c>
       <c r="B48" t="n">
-        <v>79412</v>
+        <v>79952</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5192,21 +5192,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439556</v>
+        <v>439558</v>
       </c>
       <c r="R48" t="n">
-        <v>6883244</v>
+        <v>6883256</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132852323</v>
+        <v>132849550</v>
       </c>
       <c r="B49" t="n">
-        <v>79952</v>
+        <v>79412</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5289,21 +5289,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439383</v>
+        <v>439556</v>
       </c>
       <c r="R49" t="n">
-        <v>6883628</v>
+        <v>6883244</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132853541</v>
+        <v>132851662</v>
       </c>
       <c r="B2" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439124</v>
+        <v>439581</v>
       </c>
       <c r="R2" t="n">
-        <v>6883715</v>
+        <v>6883476</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132851662</v>
+        <v>132853541</v>
       </c>
       <c r="B3" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439581</v>
+        <v>439124</v>
       </c>
       <c r="R3" t="n">
-        <v>6883476</v>
+        <v>6883715</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,59 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132853335</v>
+        <v>132853049</v>
       </c>
       <c r="B4" t="n">
-        <v>93206</v>
+        <v>79412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439146</v>
+        <v>439230</v>
       </c>
       <c r="R4" t="n">
-        <v>6883811</v>
+        <v>6883797</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -980,45 +966,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132853049</v>
+        <v>132853335</v>
       </c>
       <c r="B5" t="n">
-        <v>79412</v>
+        <v>93206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439230</v>
+        <v>439146</v>
       </c>
       <c r="R5" t="n">
-        <v>6883797</v>
+        <v>6883811</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132852304</v>
+        <v>132854923</v>
       </c>
       <c r="B10" t="n">
         <v>79412</v>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439388</v>
+        <v>439147</v>
       </c>
       <c r="R10" t="n">
-        <v>6883611</v>
+        <v>6883559</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1567,7 +1567,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132854923</v>
+        <v>132852304</v>
       </c>
       <c r="B11" t="n">
         <v>79412</v>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439147</v>
+        <v>439388</v>
       </c>
       <c r="R11" t="n">
-        <v>6883559</v>
+        <v>6883611</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132852859</v>
+        <v>132851109</v>
       </c>
       <c r="B12" t="n">
-        <v>57145</v>
+        <v>79412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439262</v>
+        <v>439620</v>
       </c>
       <c r="R12" t="n">
-        <v>6883822</v>
+        <v>6883420</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1735,11 +1735,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132851109</v>
+        <v>132852859</v>
       </c>
       <c r="B14" t="n">
-        <v>79412</v>
+        <v>57145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439620</v>
+        <v>439262</v>
       </c>
       <c r="R14" t="n">
-        <v>6883420</v>
+        <v>6883822</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1934,6 +1929,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132854672</v>
+        <v>132855316</v>
       </c>
       <c r="B15" t="n">
-        <v>79091</v>
+        <v>92518</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439113</v>
+        <v>439197</v>
       </c>
       <c r="R15" t="n">
-        <v>6883492</v>
+        <v>6883484</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2057,32 +2057,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132855316</v>
+        <v>132854581</v>
       </c>
       <c r="B16" t="n">
-        <v>92518</v>
+        <v>79952</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>760</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439197</v>
+        <v>439075</v>
       </c>
       <c r="R16" t="n">
-        <v>6883484</v>
+        <v>6883547</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132854581</v>
+        <v>132854672</v>
       </c>
       <c r="B17" t="n">
-        <v>79952</v>
+        <v>79091</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,21 +2165,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439075</v>
+        <v>439113</v>
       </c>
       <c r="R17" t="n">
-        <v>6883547</v>
+        <v>6883492</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2251,32 +2251,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132849808</v>
+        <v>132856227</v>
       </c>
       <c r="B18" t="n">
-        <v>79365</v>
+        <v>98001</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439579</v>
+        <v>439643</v>
       </c>
       <c r="R18" t="n">
-        <v>6883290</v>
+        <v>6883340</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132855166</v>
+        <v>132849808</v>
       </c>
       <c r="B19" t="n">
-        <v>80439</v>
+        <v>79365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439162</v>
+        <v>439579</v>
       </c>
       <c r="R19" t="n">
-        <v>6883543</v>
+        <v>6883290</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132851342</v>
+        <v>132855166</v>
       </c>
       <c r="B20" t="n">
-        <v>79090</v>
+        <v>80439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,21 +2456,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439612</v>
+        <v>439162</v>
       </c>
       <c r="R20" t="n">
-        <v>6883462</v>
+        <v>6883543</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132856227</v>
+        <v>132851342</v>
       </c>
       <c r="B21" t="n">
-        <v>98001</v>
+        <v>79090</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439643</v>
+        <v>439612</v>
       </c>
       <c r="R21" t="n">
-        <v>6883340</v>
+        <v>6883462</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2639,10 +2639,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132856307</v>
+        <v>132853397</v>
       </c>
       <c r="B22" t="n">
-        <v>79412</v>
+        <v>79091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,21 +2650,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439692</v>
+        <v>439117</v>
       </c>
       <c r="R22" t="n">
-        <v>6883295</v>
+        <v>6883809</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,32 +2736,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132853019</v>
+        <v>132856307</v>
       </c>
       <c r="B23" t="n">
-        <v>80467</v>
+        <v>79412</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439235</v>
+        <v>439692</v>
       </c>
       <c r="R23" t="n">
-        <v>6883808</v>
+        <v>6883295</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132853397</v>
+        <v>132853019</v>
       </c>
       <c r="B24" t="n">
-        <v>79091</v>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439117</v>
+        <v>439235</v>
       </c>
       <c r="R24" t="n">
-        <v>6883809</v>
+        <v>6883808</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132853955</v>
+        <v>132851377</v>
       </c>
       <c r="B28" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439099</v>
+        <v>439619</v>
       </c>
       <c r="R28" t="n">
-        <v>6883602</v>
+        <v>6883455</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3292,6 +3292,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3415,10 +3420,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132852187</v>
+        <v>132850734</v>
       </c>
       <c r="B30" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3426,21 +3431,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3450,10 +3455,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439386</v>
+        <v>439680</v>
       </c>
       <c r="R30" t="n">
-        <v>6883624</v>
+        <v>6883392</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3486,6 +3491,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3512,7 +3522,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132850734</v>
+        <v>132852517</v>
       </c>
       <c r="B31" t="n">
         <v>79412</v>
@@ -3547,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439680</v>
+        <v>439354</v>
       </c>
       <c r="R31" t="n">
-        <v>6883392</v>
+        <v>6883624</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3583,11 +3593,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3614,7 +3619,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132856616</v>
+        <v>132853955</v>
       </c>
       <c r="B32" t="n">
         <v>80439</v>
@@ -3649,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439678</v>
+        <v>439099</v>
       </c>
       <c r="R32" t="n">
-        <v>6883172</v>
+        <v>6883602</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3711,10 +3716,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132851377</v>
+        <v>132852187</v>
       </c>
       <c r="B33" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3722,21 +3727,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3746,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439619</v>
+        <v>439386</v>
       </c>
       <c r="R33" t="n">
-        <v>6883455</v>
+        <v>6883624</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3782,11 +3787,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3813,10 +3813,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132852517</v>
+        <v>132856616</v>
       </c>
       <c r="B34" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3824,21 +3824,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439354</v>
+        <v>439678</v>
       </c>
       <c r="R34" t="n">
-        <v>6883624</v>
+        <v>6883172</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132852715</v>
+        <v>132848943</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439316</v>
+        <v>439491</v>
       </c>
       <c r="R35" t="n">
-        <v>6883738</v>
+        <v>6883182</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4109,10 +4109,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132848943</v>
+        <v>132852715</v>
       </c>
       <c r="B37" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,21 +4120,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439491</v>
+        <v>439316</v>
       </c>
       <c r="R37" t="n">
-        <v>6883182</v>
+        <v>6883738</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4206,7 +4206,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132853499</v>
+        <v>132852930</v>
       </c>
       <c r="B38" t="n">
         <v>79412</v>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439076</v>
+        <v>439247</v>
       </c>
       <c r="R38" t="n">
-        <v>6883736</v>
+        <v>6883824</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4277,6 +4277,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4303,10 +4308,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132852930</v>
+        <v>132853884</v>
       </c>
       <c r="B39" t="n">
-        <v>79412</v>
+        <v>79365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4314,21 +4319,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4338,13 +4343,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439247</v>
+        <v>439130</v>
       </c>
       <c r="R39" t="n">
-        <v>6883824</v>
+        <v>6883643</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4374,11 +4379,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4405,10 +4405,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132853884</v>
+        <v>132853499</v>
       </c>
       <c r="B40" t="n">
-        <v>79365</v>
+        <v>79412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4416,21 +4416,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439130</v>
+        <v>439076</v>
       </c>
       <c r="R40" t="n">
-        <v>6883643</v>
+        <v>6883736</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5181,10 +5181,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132849417</v>
+        <v>132849550</v>
       </c>
       <c r="B48" t="n">
-        <v>79952</v>
+        <v>79412</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5192,21 +5192,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439558</v>
+        <v>439556</v>
       </c>
       <c r="R48" t="n">
-        <v>6883256</v>
+        <v>6883244</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132849550</v>
+        <v>132849417</v>
       </c>
       <c r="B49" t="n">
-        <v>79412</v>
+        <v>79952</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5289,21 +5289,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439556</v>
+        <v>439558</v>
       </c>
       <c r="R49" t="n">
-        <v>6883244</v>
+        <v>6883256</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132853049</v>
+        <v>132849625</v>
       </c>
       <c r="B4" t="n">
-        <v>79412</v>
+        <v>79365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439230</v>
+        <v>439587</v>
       </c>
       <c r="R4" t="n">
-        <v>6883797</v>
+        <v>6883256</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,59 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132853335</v>
+        <v>132853049</v>
       </c>
       <c r="B5" t="n">
-        <v>93206</v>
+        <v>79412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439146</v>
+        <v>439230</v>
       </c>
       <c r="R5" t="n">
-        <v>6883811</v>
+        <v>6883797</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1077,45 +1063,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132849625</v>
+        <v>132853335</v>
       </c>
       <c r="B6" t="n">
-        <v>79365</v>
+        <v>93206</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439587</v>
+        <v>439146</v>
       </c>
       <c r="R6" t="n">
-        <v>6883256</v>
+        <v>6883811</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132851109</v>
+        <v>132851780</v>
       </c>
       <c r="B12" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439620</v>
+        <v>439589</v>
       </c>
       <c r="R12" t="n">
-        <v>6883420</v>
+        <v>6883504</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132851780</v>
+        <v>132852859</v>
       </c>
       <c r="B13" t="n">
-        <v>80439</v>
+        <v>57145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439589</v>
+        <v>439262</v>
       </c>
       <c r="R13" t="n">
-        <v>6883504</v>
+        <v>6883822</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1832,6 +1832,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132852859</v>
+        <v>132851109</v>
       </c>
       <c r="B14" t="n">
-        <v>57145</v>
+        <v>79412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439262</v>
+        <v>439620</v>
       </c>
       <c r="R14" t="n">
-        <v>6883822</v>
+        <v>6883420</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1929,11 +1934,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,32 +2251,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132856227</v>
+        <v>132855166</v>
       </c>
       <c r="B18" t="n">
-        <v>98001</v>
+        <v>80439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439643</v>
+        <v>439162</v>
       </c>
       <c r="R18" t="n">
-        <v>6883340</v>
+        <v>6883543</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132849808</v>
+        <v>132851342</v>
       </c>
       <c r="B19" t="n">
-        <v>79365</v>
+        <v>79090</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439579</v>
+        <v>439612</v>
       </c>
       <c r="R19" t="n">
-        <v>6883290</v>
+        <v>6883462</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2445,32 +2445,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132855166</v>
+        <v>132856227</v>
       </c>
       <c r="B20" t="n">
-        <v>80439</v>
+        <v>98001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439162</v>
+        <v>439643</v>
       </c>
       <c r="R20" t="n">
-        <v>6883543</v>
+        <v>6883340</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132851342</v>
+        <v>132849808</v>
       </c>
       <c r="B21" t="n">
-        <v>79090</v>
+        <v>79365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439612</v>
+        <v>439579</v>
       </c>
       <c r="R21" t="n">
-        <v>6883462</v>
+        <v>6883290</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2639,32 +2639,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132853397</v>
+        <v>132853019</v>
       </c>
       <c r="B22" t="n">
-        <v>79091</v>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439117</v>
+        <v>439235</v>
       </c>
       <c r="R22" t="n">
-        <v>6883809</v>
+        <v>6883808</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132856307</v>
+        <v>132853397</v>
       </c>
       <c r="B23" t="n">
-        <v>79412</v>
+        <v>79091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439692</v>
+        <v>439117</v>
       </c>
       <c r="R23" t="n">
-        <v>6883295</v>
+        <v>6883809</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132853019</v>
+        <v>132849022</v>
       </c>
       <c r="B24" t="n">
-        <v>80467</v>
+        <v>79365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439235</v>
+        <v>439502</v>
       </c>
       <c r="R24" t="n">
-        <v>6883808</v>
+        <v>6883177</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132849022</v>
+        <v>132856307</v>
       </c>
       <c r="B25" t="n">
-        <v>79365</v>
+        <v>79412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439502</v>
+        <v>439692</v>
       </c>
       <c r="R25" t="n">
-        <v>6883177</v>
+        <v>6883295</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132852127</v>
+        <v>132853955</v>
       </c>
       <c r="B29" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3334,21 +3334,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439412</v>
+        <v>439099</v>
       </c>
       <c r="R29" t="n">
-        <v>6883600</v>
+        <v>6883602</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3420,10 +3420,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132850734</v>
+        <v>132852187</v>
       </c>
       <c r="B30" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3431,21 +3431,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439680</v>
+        <v>439386</v>
       </c>
       <c r="R30" t="n">
-        <v>6883392</v>
+        <v>6883624</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3491,11 +3491,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3522,10 +3517,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132852517</v>
+        <v>132856616</v>
       </c>
       <c r="B31" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3533,21 +3528,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3557,10 +3552,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439354</v>
+        <v>439678</v>
       </c>
       <c r="R31" t="n">
-        <v>6883624</v>
+        <v>6883172</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3619,10 +3614,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132853955</v>
+        <v>132852127</v>
       </c>
       <c r="B32" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3630,21 +3625,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3654,10 +3649,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439099</v>
+        <v>439412</v>
       </c>
       <c r="R32" t="n">
-        <v>6883602</v>
+        <v>6883600</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3716,10 +3711,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132852187</v>
+        <v>132850734</v>
       </c>
       <c r="B33" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3727,21 +3722,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3751,10 +3746,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439386</v>
+        <v>439680</v>
       </c>
       <c r="R33" t="n">
-        <v>6883624</v>
+        <v>6883392</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3787,6 +3782,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3813,10 +3813,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132856616</v>
+        <v>132852517</v>
       </c>
       <c r="B34" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3824,21 +3824,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439678</v>
+        <v>439354</v>
       </c>
       <c r="R34" t="n">
-        <v>6883172</v>
+        <v>6883624</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132848943</v>
+        <v>132851426</v>
       </c>
       <c r="B35" t="n">
-        <v>80438</v>
+        <v>79412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439491</v>
+        <v>439631</v>
       </c>
       <c r="R35" t="n">
-        <v>6883182</v>
+        <v>6883466</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -3981,6 +3981,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4007,10 +4012,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132851426</v>
+        <v>132852715</v>
       </c>
       <c r="B36" t="n">
-        <v>79412</v>
+        <v>79333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4018,21 +4023,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4042,10 +4047,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439631</v>
+        <v>439316</v>
       </c>
       <c r="R36" t="n">
-        <v>6883466</v>
+        <v>6883738</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4078,11 +4083,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4109,10 +4109,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132852715</v>
+        <v>132848943</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,21 +4120,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439316</v>
+        <v>439491</v>
       </c>
       <c r="R37" t="n">
-        <v>6883738</v>
+        <v>6883182</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4206,10 +4206,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132852930</v>
+        <v>132849181</v>
       </c>
       <c r="B38" t="n">
-        <v>79412</v>
+        <v>79090</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>439247</v>
+        <v>439494</v>
       </c>
       <c r="R38" t="n">
-        <v>6883824</v>
+        <v>6883219</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4277,11 +4277,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4502,10 +4497,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132849181</v>
+        <v>132852930</v>
       </c>
       <c r="B41" t="n">
-        <v>79090</v>
+        <v>79412</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4513,21 +4508,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4537,13 +4532,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439494</v>
+        <v>439247</v>
       </c>
       <c r="R41" t="n">
-        <v>6883219</v>
+        <v>6883824</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4573,6 +4568,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132849625</v>
+        <v>132853049</v>
       </c>
       <c r="B4" t="n">
-        <v>79365</v>
+        <v>79412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439587</v>
+        <v>439230</v>
       </c>
       <c r="R4" t="n">
-        <v>6883256</v>
+        <v>6883797</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,45 +966,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132853049</v>
+        <v>132853335</v>
       </c>
       <c r="B5" t="n">
-        <v>79412</v>
+        <v>93206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439230</v>
+        <v>439146</v>
       </c>
       <c r="R5" t="n">
-        <v>6883797</v>
+        <v>6883811</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,59 +1077,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132853335</v>
+        <v>132849625</v>
       </c>
       <c r="B6" t="n">
-        <v>93206</v>
+        <v>79365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439146</v>
+        <v>439587</v>
       </c>
       <c r="R6" t="n">
-        <v>6883811</v>
+        <v>6883256</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1174,32 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132851231</v>
+        <v>132852732</v>
       </c>
       <c r="B7" t="n">
-        <v>79412</v>
+        <v>57145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439625</v>
+        <v>439310</v>
       </c>
       <c r="R7" t="n">
-        <v>6883432</v>
+        <v>6883738</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1245,6 +1245,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1271,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132852732</v>
+        <v>132851231</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>79412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439310</v>
+        <v>439625</v>
       </c>
       <c r="R8" t="n">
-        <v>6883738</v>
+        <v>6883432</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1342,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2639,32 +2639,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132853019</v>
+        <v>132856307</v>
       </c>
       <c r="B22" t="n">
-        <v>80467</v>
+        <v>79412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439235</v>
+        <v>439692</v>
       </c>
       <c r="R22" t="n">
-        <v>6883808</v>
+        <v>6883295</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,32 +2736,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132853397</v>
+        <v>132853019</v>
       </c>
       <c r="B23" t="n">
-        <v>79091</v>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439117</v>
+        <v>439235</v>
       </c>
       <c r="R23" t="n">
-        <v>6883809</v>
+        <v>6883808</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132849022</v>
+        <v>132853397</v>
       </c>
       <c r="B24" t="n">
-        <v>79365</v>
+        <v>79091</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439502</v>
+        <v>439117</v>
       </c>
       <c r="R24" t="n">
-        <v>6883177</v>
+        <v>6883809</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132856307</v>
+        <v>132849022</v>
       </c>
       <c r="B25" t="n">
-        <v>79412</v>
+        <v>79365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439692</v>
+        <v>439502</v>
       </c>
       <c r="R25" t="n">
-        <v>6883295</v>
+        <v>6883177</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132851426</v>
+        <v>132848943</v>
       </c>
       <c r="B35" t="n">
-        <v>79412</v>
+        <v>80438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439631</v>
+        <v>439491</v>
       </c>
       <c r="R35" t="n">
-        <v>6883466</v>
+        <v>6883182</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -3981,11 +3981,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4012,10 +4007,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132852715</v>
+        <v>132851426</v>
       </c>
       <c r="B36" t="n">
-        <v>79333</v>
+        <v>79412</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4023,21 +4018,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4047,10 +4042,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439316</v>
+        <v>439631</v>
       </c>
       <c r="R36" t="n">
-        <v>6883738</v>
+        <v>6883466</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4083,6 +4078,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4109,10 +4109,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132848943</v>
+        <v>132852715</v>
       </c>
       <c r="B37" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,21 +4120,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439491</v>
+        <v>439316</v>
       </c>
       <c r="R37" t="n">
-        <v>6883182</v>
+        <v>6883738</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132853049</v>
+        <v>132849625</v>
       </c>
       <c r="B4" t="n">
-        <v>79412</v>
+        <v>79365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439230</v>
+        <v>439587</v>
       </c>
       <c r="R4" t="n">
-        <v>6883797</v>
+        <v>6883256</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,59 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132853335</v>
+        <v>132853049</v>
       </c>
       <c r="B5" t="n">
-        <v>93206</v>
+        <v>79412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439146</v>
+        <v>439230</v>
       </c>
       <c r="R5" t="n">
-        <v>6883811</v>
+        <v>6883797</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1077,45 +1063,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132849625</v>
+        <v>132853335</v>
       </c>
       <c r="B6" t="n">
-        <v>79365</v>
+        <v>93206</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439587</v>
+        <v>439146</v>
       </c>
       <c r="R6" t="n">
-        <v>6883256</v>
+        <v>6883811</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132851780</v>
+        <v>132851109</v>
       </c>
       <c r="B12" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439589</v>
+        <v>439620</v>
       </c>
       <c r="R12" t="n">
-        <v>6883504</v>
+        <v>6883420</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132852859</v>
+        <v>132851780</v>
       </c>
       <c r="B13" t="n">
-        <v>57145</v>
+        <v>80439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439262</v>
+        <v>439589</v>
       </c>
       <c r="R13" t="n">
-        <v>6883822</v>
+        <v>6883504</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1832,11 +1832,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1863,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132851109</v>
+        <v>132852859</v>
       </c>
       <c r="B14" t="n">
-        <v>79412</v>
+        <v>57145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439620</v>
+        <v>439262</v>
       </c>
       <c r="R14" t="n">
-        <v>6883420</v>
+        <v>6883822</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1934,6 +1929,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132849625</v>
+        <v>132853049</v>
       </c>
       <c r="B4" t="n">
-        <v>79365</v>
+        <v>79412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439587</v>
+        <v>439230</v>
       </c>
       <c r="R4" t="n">
-        <v>6883256</v>
+        <v>6883797</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,45 +966,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132853049</v>
+        <v>132853335</v>
       </c>
       <c r="B5" t="n">
-        <v>79412</v>
+        <v>93206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439230</v>
+        <v>439146</v>
       </c>
       <c r="R5" t="n">
-        <v>6883797</v>
+        <v>6883811</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,59 +1077,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132853335</v>
+        <v>132849625</v>
       </c>
       <c r="B6" t="n">
-        <v>93206</v>
+        <v>79365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439146</v>
+        <v>439587</v>
       </c>
       <c r="R6" t="n">
-        <v>6883811</v>
+        <v>6883256</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1174,32 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132852732</v>
+        <v>132851231</v>
       </c>
       <c r="B7" t="n">
-        <v>57145</v>
+        <v>79412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439310</v>
+        <v>439625</v>
       </c>
       <c r="R7" t="n">
-        <v>6883738</v>
+        <v>6883432</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1245,11 +1245,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,32 +1271,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132851231</v>
+        <v>132852732</v>
       </c>
       <c r="B8" t="n">
-        <v>79412</v>
+        <v>57145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439625</v>
+        <v>439310</v>
       </c>
       <c r="R8" t="n">
-        <v>6883432</v>
+        <v>6883738</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1347,6 +1342,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132851109</v>
+        <v>132851780</v>
       </c>
       <c r="B12" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,21 +1675,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439620</v>
+        <v>439589</v>
       </c>
       <c r="R12" t="n">
-        <v>6883420</v>
+        <v>6883504</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132851780</v>
+        <v>132852859</v>
       </c>
       <c r="B13" t="n">
-        <v>80439</v>
+        <v>57145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439589</v>
+        <v>439262</v>
       </c>
       <c r="R13" t="n">
-        <v>6883504</v>
+        <v>6883822</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1832,6 +1832,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132852859</v>
+        <v>132851109</v>
       </c>
       <c r="B14" t="n">
-        <v>57145</v>
+        <v>79412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439262</v>
+        <v>439620</v>
       </c>
       <c r="R14" t="n">
-        <v>6883822</v>
+        <v>6883420</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1929,11 +1934,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,32 +2251,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132855166</v>
+        <v>132856227</v>
       </c>
       <c r="B18" t="n">
-        <v>80439</v>
+        <v>98001</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439162</v>
+        <v>439643</v>
       </c>
       <c r="R18" t="n">
-        <v>6883543</v>
+        <v>6883340</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132851342</v>
+        <v>132849808</v>
       </c>
       <c r="B19" t="n">
-        <v>79090</v>
+        <v>79365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439612</v>
+        <v>439579</v>
       </c>
       <c r="R19" t="n">
-        <v>6883462</v>
+        <v>6883290</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2445,32 +2445,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132856227</v>
+        <v>132855166</v>
       </c>
       <c r="B20" t="n">
-        <v>98001</v>
+        <v>80439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439643</v>
+        <v>439162</v>
       </c>
       <c r="R20" t="n">
-        <v>6883340</v>
+        <v>6883543</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132849808</v>
+        <v>132851342</v>
       </c>
       <c r="B21" t="n">
-        <v>79365</v>
+        <v>79090</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439579</v>
+        <v>439612</v>
       </c>
       <c r="R21" t="n">
-        <v>6883290</v>
+        <v>6883462</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2639,32 +2639,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132856307</v>
+        <v>132853019</v>
       </c>
       <c r="B22" t="n">
-        <v>79412</v>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439692</v>
+        <v>439235</v>
       </c>
       <c r="R22" t="n">
-        <v>6883295</v>
+        <v>6883808</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,32 +2736,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132853019</v>
+        <v>132853397</v>
       </c>
       <c r="B23" t="n">
-        <v>80467</v>
+        <v>79091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439235</v>
+        <v>439117</v>
       </c>
       <c r="R23" t="n">
-        <v>6883808</v>
+        <v>6883809</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132853397</v>
+        <v>132849022</v>
       </c>
       <c r="B24" t="n">
-        <v>79091</v>
+        <v>79365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439117</v>
+        <v>439502</v>
       </c>
       <c r="R24" t="n">
-        <v>6883809</v>
+        <v>6883177</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132849022</v>
+        <v>132856307</v>
       </c>
       <c r="B25" t="n">
-        <v>79365</v>
+        <v>79412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439502</v>
+        <v>439692</v>
       </c>
       <c r="R25" t="n">
-        <v>6883177</v>
+        <v>6883295</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132853955</v>
+        <v>132852127</v>
       </c>
       <c r="B29" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3334,21 +3334,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439099</v>
+        <v>439412</v>
       </c>
       <c r="R29" t="n">
-        <v>6883602</v>
+        <v>6883600</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3420,10 +3420,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132852187</v>
+        <v>132850734</v>
       </c>
       <c r="B30" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3431,21 +3431,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439386</v>
+        <v>439680</v>
       </c>
       <c r="R30" t="n">
-        <v>6883624</v>
+        <v>6883392</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3491,6 +3491,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3517,10 +3522,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132856616</v>
+        <v>132852517</v>
       </c>
       <c r="B31" t="n">
-        <v>80439</v>
+        <v>79412</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3528,21 +3533,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3552,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439678</v>
+        <v>439354</v>
       </c>
       <c r="R31" t="n">
-        <v>6883172</v>
+        <v>6883624</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3614,10 +3619,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132852127</v>
+        <v>132853955</v>
       </c>
       <c r="B32" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3625,21 +3630,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3649,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439412</v>
+        <v>439099</v>
       </c>
       <c r="R32" t="n">
-        <v>6883600</v>
+        <v>6883602</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3711,10 +3716,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132850734</v>
+        <v>132852187</v>
       </c>
       <c r="B33" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3722,21 +3727,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3746,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439680</v>
+        <v>439386</v>
       </c>
       <c r="R33" t="n">
-        <v>6883392</v>
+        <v>6883624</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3782,11 +3787,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3813,10 +3813,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132852517</v>
+        <v>132856616</v>
       </c>
       <c r="B34" t="n">
-        <v>79412</v>
+        <v>80439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3824,21 +3824,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439354</v>
+        <v>439678</v>
       </c>
       <c r="R34" t="n">
-        <v>6883624</v>
+        <v>6883172</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132848943</v>
+        <v>132851426</v>
       </c>
       <c r="B35" t="n">
-        <v>80438</v>
+        <v>79412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439491</v>
+        <v>439631</v>
       </c>
       <c r="R35" t="n">
-        <v>6883182</v>
+        <v>6883466</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -3981,6 +3981,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4007,10 +4012,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132851426</v>
+        <v>132852715</v>
       </c>
       <c r="B36" t="n">
-        <v>79412</v>
+        <v>79333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4018,21 +4023,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4042,10 +4047,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439631</v>
+        <v>439316</v>
       </c>
       <c r="R36" t="n">
-        <v>6883466</v>
+        <v>6883738</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4078,11 +4083,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4109,10 +4109,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132852715</v>
+        <v>132848943</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,21 +4120,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439316</v>
+        <v>439491</v>
       </c>
       <c r="R37" t="n">
-        <v>6883738</v>
+        <v>6883182</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132851662</v>
+        <v>132853541</v>
       </c>
       <c r="B2" t="n">
-        <v>79412</v>
+        <v>80440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439581</v>
+        <v>439124</v>
       </c>
       <c r="R2" t="n">
-        <v>6883476</v>
+        <v>6883715</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132853541</v>
+        <v>132851662</v>
       </c>
       <c r="B3" t="n">
-        <v>80439</v>
+        <v>79413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439124</v>
+        <v>439581</v>
       </c>
       <c r="R3" t="n">
-        <v>6883715</v>
+        <v>6883476</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132853049</v>
+        <v>132849625</v>
       </c>
       <c r="B4" t="n">
-        <v>79412</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439230</v>
+        <v>439587</v>
       </c>
       <c r="R4" t="n">
-        <v>6883797</v>
+        <v>6883256</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -969,7 +969,7 @@
         <v>132853335</v>
       </c>
       <c r="B5" t="n">
-        <v>93206</v>
+        <v>93208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132849625</v>
+        <v>132853049</v>
       </c>
       <c r="B6" t="n">
-        <v>79365</v>
+        <v>79413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,21 +1088,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439587</v>
+        <v>439230</v>
       </c>
       <c r="R6" t="n">
-        <v>6883256</v>
+        <v>6883797</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1174,32 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132851231</v>
+        <v>132852732</v>
       </c>
       <c r="B7" t="n">
-        <v>79412</v>
+        <v>57145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439625</v>
+        <v>439310</v>
       </c>
       <c r="R7" t="n">
-        <v>6883432</v>
+        <v>6883738</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1245,6 +1245,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1271,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132852732</v>
+        <v>132852203</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>79924</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439310</v>
+        <v>439393</v>
       </c>
       <c r="R8" t="n">
-        <v>6883738</v>
+        <v>6883615</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1342,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132852203</v>
+        <v>132851231</v>
       </c>
       <c r="B9" t="n">
-        <v>79923</v>
+        <v>79413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439393</v>
+        <v>439625</v>
       </c>
       <c r="R9" t="n">
-        <v>6883615</v>
+        <v>6883432</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132854923</v>
+        <v>132852304</v>
       </c>
       <c r="B10" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439147</v>
+        <v>439388</v>
       </c>
       <c r="R10" t="n">
-        <v>6883559</v>
+        <v>6883611</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1567,10 +1567,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132852304</v>
+        <v>132854923</v>
       </c>
       <c r="B11" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439388</v>
+        <v>439147</v>
       </c>
       <c r="R11" t="n">
-        <v>6883611</v>
+        <v>6883559</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1664,32 +1664,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132851780</v>
+        <v>132852859</v>
       </c>
       <c r="B12" t="n">
-        <v>80439</v>
+        <v>57145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439589</v>
+        <v>439262</v>
       </c>
       <c r="R12" t="n">
-        <v>6883504</v>
+        <v>6883822</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1735,6 +1735,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,32 +1766,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132852859</v>
+        <v>132851780</v>
       </c>
       <c r="B13" t="n">
-        <v>57145</v>
+        <v>80440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439262</v>
+        <v>439589</v>
       </c>
       <c r="R13" t="n">
-        <v>6883822</v>
+        <v>6883504</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1832,11 +1837,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,7 +1866,7 @@
         <v>132851109</v>
       </c>
       <c r="B14" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132855316</v>
+        <v>132854672</v>
       </c>
       <c r="B15" t="n">
-        <v>92518</v>
+        <v>79092</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439197</v>
+        <v>439113</v>
       </c>
       <c r="R15" t="n">
-        <v>6883484</v>
+        <v>6883492</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2060,7 +2060,7 @@
         <v>132854581</v>
       </c>
       <c r="B16" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,32 +2154,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132854672</v>
+        <v>132855316</v>
       </c>
       <c r="B17" t="n">
-        <v>79091</v>
+        <v>92520</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>760</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439113</v>
+        <v>439197</v>
       </c>
       <c r="R17" t="n">
-        <v>6883492</v>
+        <v>6883484</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2254,7 +2254,7 @@
         <v>132856227</v>
       </c>
       <c r="B18" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>132849808</v>
       </c>
       <c r="B19" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132855166</v>
+        <v>132851342</v>
       </c>
       <c r="B20" t="n">
-        <v>80439</v>
+        <v>79091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,21 +2456,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439162</v>
+        <v>439612</v>
       </c>
       <c r="R20" t="n">
-        <v>6883543</v>
+        <v>6883462</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132851342</v>
+        <v>132855166</v>
       </c>
       <c r="B21" t="n">
-        <v>79090</v>
+        <v>80440</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439612</v>
+        <v>439162</v>
       </c>
       <c r="R21" t="n">
-        <v>6883462</v>
+        <v>6883543</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2639,32 +2639,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132853019</v>
+        <v>132853397</v>
       </c>
       <c r="B22" t="n">
-        <v>80467</v>
+        <v>79092</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439235</v>
+        <v>439117</v>
       </c>
       <c r="R22" t="n">
-        <v>6883808</v>
+        <v>6883809</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132853397</v>
+        <v>132849022</v>
       </c>
       <c r="B23" t="n">
-        <v>79091</v>
+        <v>79366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439117</v>
+        <v>439502</v>
       </c>
       <c r="R23" t="n">
-        <v>6883809</v>
+        <v>6883177</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132849022</v>
+        <v>132853019</v>
       </c>
       <c r="B24" t="n">
-        <v>79365</v>
+        <v>80468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439502</v>
+        <v>439235</v>
       </c>
       <c r="R24" t="n">
-        <v>6883177</v>
+        <v>6883808</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2933,7 +2933,7 @@
         <v>132856307</v>
       </c>
       <c r="B25" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>132851904</v>
       </c>
       <c r="B26" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>132848062</v>
       </c>
       <c r="B27" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132851377</v>
+        <v>132853955</v>
       </c>
       <c r="B28" t="n">
-        <v>79412</v>
+        <v>80440</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439619</v>
+        <v>439099</v>
       </c>
       <c r="R28" t="n">
-        <v>6883455</v>
+        <v>6883602</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3292,11 +3292,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3326,7 +3321,7 @@
         <v>132852127</v>
       </c>
       <c r="B29" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3420,10 +3415,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132850734</v>
+        <v>132852187</v>
       </c>
       <c r="B30" t="n">
-        <v>79412</v>
+        <v>80440</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3431,21 +3426,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3455,10 +3450,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439680</v>
+        <v>439386</v>
       </c>
       <c r="R30" t="n">
-        <v>6883392</v>
+        <v>6883624</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3491,11 +3486,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3522,10 +3512,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132852517</v>
+        <v>132850734</v>
       </c>
       <c r="B31" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3557,10 +3547,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439354</v>
+        <v>439680</v>
       </c>
       <c r="R31" t="n">
-        <v>6883624</v>
+        <v>6883392</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3593,6 +3583,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3619,10 +3614,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132853955</v>
+        <v>132856616</v>
       </c>
       <c r="B32" t="n">
-        <v>80439</v>
+        <v>80440</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3654,10 +3649,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439099</v>
+        <v>439678</v>
       </c>
       <c r="R32" t="n">
-        <v>6883602</v>
+        <v>6883172</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3716,10 +3711,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132852187</v>
+        <v>132851377</v>
       </c>
       <c r="B33" t="n">
-        <v>80439</v>
+        <v>79413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3727,21 +3722,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3751,10 +3746,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439386</v>
+        <v>439619</v>
       </c>
       <c r="R33" t="n">
-        <v>6883624</v>
+        <v>6883455</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3787,6 +3782,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3813,10 +3813,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132856616</v>
+        <v>132852517</v>
       </c>
       <c r="B34" t="n">
-        <v>80439</v>
+        <v>79413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3824,21 +3824,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439678</v>
+        <v>439354</v>
       </c>
       <c r="R34" t="n">
-        <v>6883172</v>
+        <v>6883624</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3913,7 +3913,7 @@
         <v>132851426</v>
       </c>
       <c r="B35" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132852715</v>
+        <v>132848943</v>
       </c>
       <c r="B36" t="n">
-        <v>79333</v>
+        <v>80439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4023,21 +4023,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4047,10 +4047,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439316</v>
+        <v>439491</v>
       </c>
       <c r="R36" t="n">
-        <v>6883738</v>
+        <v>6883182</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4109,10 +4109,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132848943</v>
+        <v>132852715</v>
       </c>
       <c r="B37" t="n">
-        <v>80438</v>
+        <v>79334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,21 +4120,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439491</v>
+        <v>439316</v>
       </c>
       <c r="R37" t="n">
-        <v>6883182</v>
+        <v>6883738</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4209,7 +4209,7 @@
         <v>132849181</v>
       </c>
       <c r="B38" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4303,10 +4303,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132853884</v>
+        <v>132853499</v>
       </c>
       <c r="B39" t="n">
-        <v>79365</v>
+        <v>79413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4314,21 +4314,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439130</v>
+        <v>439076</v>
       </c>
       <c r="R39" t="n">
-        <v>6883643</v>
+        <v>6883736</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4400,10 +4400,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132853499</v>
+        <v>132852930</v>
       </c>
       <c r="B40" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4435,13 +4435,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439076</v>
+        <v>439247</v>
       </c>
       <c r="R40" t="n">
-        <v>6883736</v>
+        <v>6883824</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4471,6 +4471,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4497,10 +4502,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132852930</v>
+        <v>132853884</v>
       </c>
       <c r="B41" t="n">
-        <v>79412</v>
+        <v>79366</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4508,21 +4513,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4532,13 +4537,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439247</v>
+        <v>439130</v>
       </c>
       <c r="R41" t="n">
-        <v>6883824</v>
+        <v>6883643</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4568,11 +4573,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4602,7 +4602,7 @@
         <v>132851614</v>
       </c>
       <c r="B42" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>132851872</v>
       </c>
       <c r="B43" t="n">
-        <v>80439</v>
+        <v>80440</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>132847930</v>
       </c>
       <c r="B44" t="n">
-        <v>80439</v>
+        <v>80440</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>132849316</v>
       </c>
       <c r="B45" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>132848015</v>
       </c>
       <c r="B46" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5084,10 +5084,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132852323</v>
+        <v>132849550</v>
       </c>
       <c r="B47" t="n">
-        <v>79952</v>
+        <v>79413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5095,21 +5095,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439383</v>
+        <v>439556</v>
       </c>
       <c r="R47" t="n">
-        <v>6883628</v>
+        <v>6883244</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5181,10 +5181,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132849550</v>
+        <v>132849417</v>
       </c>
       <c r="B48" t="n">
-        <v>79412</v>
+        <v>79953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5192,21 +5192,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439556</v>
+        <v>439558</v>
       </c>
       <c r="R48" t="n">
-        <v>6883244</v>
+        <v>6883256</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132849417</v>
+        <v>132852323</v>
       </c>
       <c r="B49" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439558</v>
+        <v>439383</v>
       </c>
       <c r="R49" t="n">
-        <v>6883256</v>
+        <v>6883628</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5480,7 +5480,7 @@
         <v>132849144</v>
       </c>
       <c r="B51" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132849625</v>
+        <v>132853049</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>79413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439587</v>
+        <v>439230</v>
       </c>
       <c r="R4" t="n">
-        <v>6883256</v>
+        <v>6883797</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,59 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132853335</v>
+        <v>132849625</v>
       </c>
       <c r="B5" t="n">
-        <v>93208</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439146</v>
+        <v>439587</v>
       </c>
       <c r="R5" t="n">
-        <v>6883811</v>
+        <v>6883256</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1077,45 +1063,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132853049</v>
+        <v>132853335</v>
       </c>
       <c r="B6" t="n">
-        <v>79413</v>
+        <v>93208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439230</v>
+        <v>439146</v>
       </c>
       <c r="R6" t="n">
-        <v>6883797</v>
+        <v>6883811</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1174,32 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132852732</v>
+        <v>132852203</v>
       </c>
       <c r="B7" t="n">
-        <v>57145</v>
+        <v>79924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439310</v>
+        <v>439393</v>
       </c>
       <c r="R7" t="n">
-        <v>6883738</v>
+        <v>6883615</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1245,11 +1245,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,32 +1271,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132852203</v>
+        <v>132852732</v>
       </c>
       <c r="B8" t="n">
-        <v>79924</v>
+        <v>57145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439393</v>
+        <v>439310</v>
       </c>
       <c r="R8" t="n">
-        <v>6883615</v>
+        <v>6883738</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1347,6 +1342,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1960,10 +1960,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132854672</v>
+        <v>132854581</v>
       </c>
       <c r="B15" t="n">
-        <v>79092</v>
+        <v>79953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,21 +1971,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439113</v>
+        <v>439075</v>
       </c>
       <c r="R15" t="n">
-        <v>6883492</v>
+        <v>6883547</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2057,32 +2057,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132854581</v>
+        <v>132855316</v>
       </c>
       <c r="B16" t="n">
-        <v>79953</v>
+        <v>92520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>760</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2092,10 +2092,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439075</v>
+        <v>439197</v>
       </c>
       <c r="R16" t="n">
-        <v>6883547</v>
+        <v>6883484</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2154,32 +2154,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132855316</v>
+        <v>132854672</v>
       </c>
       <c r="B17" t="n">
-        <v>92520</v>
+        <v>79092</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>760</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439197</v>
+        <v>439113</v>
       </c>
       <c r="R17" t="n">
-        <v>6883484</v>
+        <v>6883492</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2251,32 +2251,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132856227</v>
+        <v>132849808</v>
       </c>
       <c r="B18" t="n">
-        <v>98003</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439643</v>
+        <v>439579</v>
       </c>
       <c r="R18" t="n">
-        <v>6883340</v>
+        <v>6883290</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132849808</v>
+        <v>132851342</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79091</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439579</v>
+        <v>439612</v>
       </c>
       <c r="R19" t="n">
-        <v>6883290</v>
+        <v>6883462</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132851342</v>
+        <v>132855166</v>
       </c>
       <c r="B20" t="n">
-        <v>79091</v>
+        <v>80440</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,21 +2456,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439612</v>
+        <v>439162</v>
       </c>
       <c r="R20" t="n">
-        <v>6883462</v>
+        <v>6883543</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132855166</v>
+        <v>132856227</v>
       </c>
       <c r="B21" t="n">
-        <v>80440</v>
+        <v>98003</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439162</v>
+        <v>439643</v>
       </c>
       <c r="R21" t="n">
-        <v>6883543</v>
+        <v>6883340</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2639,10 +2639,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132853397</v>
+        <v>132849022</v>
       </c>
       <c r="B22" t="n">
-        <v>79092</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,21 +2650,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439117</v>
+        <v>439502</v>
       </c>
       <c r="R22" t="n">
-        <v>6883809</v>
+        <v>6883177</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,32 +2736,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132849022</v>
+        <v>132853019</v>
       </c>
       <c r="B23" t="n">
-        <v>79366</v>
+        <v>80468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439502</v>
+        <v>439235</v>
       </c>
       <c r="R23" t="n">
-        <v>6883177</v>
+        <v>6883808</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,32 +2833,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132853019</v>
+        <v>132856307</v>
       </c>
       <c r="B24" t="n">
-        <v>80468</v>
+        <v>79413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439235</v>
+        <v>439692</v>
       </c>
       <c r="R24" t="n">
-        <v>6883808</v>
+        <v>6883295</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132856307</v>
+        <v>132853397</v>
       </c>
       <c r="B25" t="n">
-        <v>79413</v>
+        <v>79092</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>864</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439692</v>
+        <v>439117</v>
       </c>
       <c r="R25" t="n">
-        <v>6883295</v>
+        <v>6883809</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132851426</v>
+        <v>132852715</v>
       </c>
       <c r="B35" t="n">
-        <v>79413</v>
+        <v>79334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3921,21 +3921,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>439631</v>
+        <v>439316</v>
       </c>
       <c r="R35" t="n">
-        <v>6883466</v>
+        <v>6883738</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -3981,11 +3981,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4012,10 +4007,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132848943</v>
+        <v>132851426</v>
       </c>
       <c r="B36" t="n">
-        <v>80439</v>
+        <v>79413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4023,21 +4018,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4047,10 +4042,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439491</v>
+        <v>439631</v>
       </c>
       <c r="R36" t="n">
-        <v>6883182</v>
+        <v>6883466</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4083,6 +4078,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4109,10 +4109,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132852715</v>
+        <v>132848943</v>
       </c>
       <c r="B37" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,21 +4120,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4144,10 +4144,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439316</v>
+        <v>439491</v>
       </c>
       <c r="R37" t="n">
-        <v>6883738</v>
+        <v>6883182</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132847930</v>
+        <v>132849316</v>
       </c>
       <c r="B44" t="n">
-        <v>80440</v>
+        <v>79413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4804,21 +4804,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4828,13 +4828,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439521</v>
+        <v>439497</v>
       </c>
       <c r="R44" t="n">
-        <v>6883085</v>
+        <v>6883243</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132849316</v>
+        <v>132848015</v>
       </c>
       <c r="B45" t="n">
         <v>79413</v>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439497</v>
+        <v>439534</v>
       </c>
       <c r="R45" t="n">
-        <v>6883243</v>
+        <v>6883074</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132848015</v>
+        <v>132847930</v>
       </c>
       <c r="B46" t="n">
-        <v>79413</v>
+        <v>80440</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4998,21 +4998,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439534</v>
+        <v>439521</v>
       </c>
       <c r="R46" t="n">
-        <v>6883074</v>
+        <v>6883085</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5084,10 +5084,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132849550</v>
+        <v>132852323</v>
       </c>
       <c r="B47" t="n">
-        <v>79413</v>
+        <v>79953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5095,21 +5095,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439556</v>
+        <v>439383</v>
       </c>
       <c r="R47" t="n">
-        <v>6883244</v>
+        <v>6883628</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5181,10 +5181,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132849417</v>
+        <v>132849550</v>
       </c>
       <c r="B48" t="n">
-        <v>79953</v>
+        <v>79413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5192,21 +5192,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5216,10 +5216,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439558</v>
+        <v>439556</v>
       </c>
       <c r="R48" t="n">
-        <v>6883256</v>
+        <v>6883244</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132852323</v>
+        <v>132849417</v>
       </c>
       <c r="B49" t="n">
         <v>79953</v>
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439383</v>
+        <v>439558</v>
       </c>
       <c r="R49" t="n">
-        <v>6883628</v>
+        <v>6883256</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132853541</v>
+        <v>132849022</v>
       </c>
       <c r="B2" t="n">
-        <v>80440</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439124</v>
+        <v>439502</v>
       </c>
       <c r="R2" t="n">
-        <v>6883715</v>
+        <v>6883177</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132851662</v>
+        <v>132849625</v>
       </c>
       <c r="B3" t="n">
-        <v>79413</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439581</v>
+        <v>439587</v>
       </c>
       <c r="R3" t="n">
-        <v>6883476</v>
+        <v>6883256</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132853049</v>
+        <v>132849808</v>
       </c>
       <c r="B4" t="n">
-        <v>79413</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439230</v>
+        <v>439579</v>
       </c>
       <c r="R4" t="n">
-        <v>6883797</v>
+        <v>6883290</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132849625</v>
+        <v>132853884</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439587</v>
+        <v>439130</v>
       </c>
       <c r="R5" t="n">
-        <v>6883256</v>
+        <v>6883643</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,59 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132853335</v>
+        <v>132855316</v>
       </c>
       <c r="B6" t="n">
-        <v>93208</v>
+        <v>92546</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439146</v>
+        <v>439197</v>
       </c>
       <c r="R6" t="n">
-        <v>6883811</v>
+        <v>6883484</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1174,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132852203</v>
+        <v>132848015</v>
       </c>
       <c r="B7" t="n">
-        <v>79924</v>
+        <v>79452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1185,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439393</v>
+        <v>439534</v>
       </c>
       <c r="R7" t="n">
-        <v>6883615</v>
+        <v>6883074</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1271,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132852732</v>
+        <v>132849316</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>79452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439310</v>
+        <v>439497</v>
       </c>
       <c r="R8" t="n">
-        <v>6883738</v>
+        <v>6883243</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1342,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132851231</v>
+        <v>132849550</v>
       </c>
       <c r="B9" t="n">
-        <v>79413</v>
+        <v>79452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439625</v>
+        <v>439556</v>
       </c>
       <c r="R9" t="n">
-        <v>6883432</v>
+        <v>6883244</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1470,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132852304</v>
+        <v>132850734</v>
       </c>
       <c r="B10" t="n">
-        <v>79413</v>
+        <v>79452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439388</v>
+        <v>439680</v>
       </c>
       <c r="R10" t="n">
-        <v>6883611</v>
+        <v>6883392</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1541,6 +1522,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1567,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132854923</v>
+        <v>132851109</v>
       </c>
       <c r="B11" t="n">
-        <v>79413</v>
+        <v>79452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439147</v>
+        <v>439620</v>
       </c>
       <c r="R11" t="n">
-        <v>6883559</v>
+        <v>6883420</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1664,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132852859</v>
+        <v>132851231</v>
       </c>
       <c r="B12" t="n">
-        <v>57145</v>
+        <v>79452</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1699,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439262</v>
+        <v>439625</v>
       </c>
       <c r="R12" t="n">
-        <v>6883822</v>
+        <v>6883432</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1735,11 +1721,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1766,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132851780</v>
+        <v>132851377</v>
       </c>
       <c r="B13" t="n">
-        <v>80440</v>
+        <v>79452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1801,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439589</v>
+        <v>439619</v>
       </c>
       <c r="R13" t="n">
-        <v>6883504</v>
+        <v>6883455</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1837,6 +1818,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1863,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132851109</v>
+        <v>132851426</v>
       </c>
       <c r="B14" t="n">
-        <v>79413</v>
+        <v>79452</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439620</v>
+        <v>439631</v>
       </c>
       <c r="R14" t="n">
-        <v>6883420</v>
+        <v>6883466</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1934,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1960,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132854581</v>
+        <v>132851614</v>
       </c>
       <c r="B15" t="n">
-        <v>79953</v>
+        <v>79452</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439075</v>
+        <v>439614</v>
       </c>
       <c r="R15" t="n">
-        <v>6883547</v>
+        <v>6883457</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2057,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132855316</v>
+        <v>132851662</v>
       </c>
       <c r="B16" t="n">
-        <v>92520</v>
+        <v>79452</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>760</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2092,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439197</v>
+        <v>439581</v>
       </c>
       <c r="R16" t="n">
-        <v>6883484</v>
+        <v>6883476</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2154,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132854672</v>
+        <v>132851904</v>
       </c>
       <c r="B17" t="n">
-        <v>79092</v>
+        <v>79452</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439113</v>
+        <v>439510</v>
       </c>
       <c r="R17" t="n">
-        <v>6883492</v>
+        <v>6883560</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2251,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132849808</v>
+        <v>132852127</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>79452</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2286,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439579</v>
+        <v>439412</v>
       </c>
       <c r="R18" t="n">
-        <v>6883290</v>
+        <v>6883600</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2348,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132851342</v>
+        <v>132852304</v>
       </c>
       <c r="B19" t="n">
-        <v>79091</v>
+        <v>79452</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2383,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439612</v>
+        <v>439388</v>
       </c>
       <c r="R19" t="n">
-        <v>6883462</v>
+        <v>6883611</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2445,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132855166</v>
+        <v>132852517</v>
       </c>
       <c r="B20" t="n">
-        <v>80440</v>
+        <v>79452</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2480,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439162</v>
+        <v>439354</v>
       </c>
       <c r="R20" t="n">
-        <v>6883543</v>
+        <v>6883624</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2542,32 +2533,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132856227</v>
+        <v>132852930</v>
       </c>
       <c r="B21" t="n">
-        <v>98003</v>
+        <v>79452</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2577,13 +2568,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439643</v>
+        <v>439247</v>
       </c>
       <c r="R21" t="n">
-        <v>6883340</v>
+        <v>6883824</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2613,6 +2604,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2639,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132849022</v>
+        <v>132853049</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>79452</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2674,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>439502</v>
+        <v>439230</v>
       </c>
       <c r="R22" t="n">
-        <v>6883177</v>
+        <v>6883797</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2736,32 +2732,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132853019</v>
+        <v>132853499</v>
       </c>
       <c r="B23" t="n">
-        <v>80468</v>
+        <v>79452</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>864</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2771,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>439235</v>
+        <v>439076</v>
       </c>
       <c r="R23" t="n">
-        <v>6883808</v>
+        <v>6883736</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2833,10 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132856307</v>
+        <v>132854923</v>
       </c>
       <c r="B24" t="n">
-        <v>79413</v>
+        <v>79452</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>439692</v>
+        <v>439147</v>
       </c>
       <c r="R24" t="n">
-        <v>6883295</v>
+        <v>6883559</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2930,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132853397</v>
+        <v>132856307</v>
       </c>
       <c r="B25" t="n">
-        <v>79092</v>
+        <v>79452</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2965,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>439117</v>
+        <v>439692</v>
       </c>
       <c r="R25" t="n">
-        <v>6883809</v>
+        <v>6883295</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3027,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132851904</v>
+        <v>132847930</v>
       </c>
       <c r="B26" t="n">
-        <v>79413</v>
+        <v>80489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3038,21 +3034,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3062,13 +3058,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>439510</v>
+        <v>439521</v>
       </c>
       <c r="R26" t="n">
-        <v>6883560</v>
+        <v>6883085</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3124,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132848062</v>
+        <v>132851780</v>
       </c>
       <c r="B27" t="n">
-        <v>79091</v>
+        <v>80489</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3135,21 +3131,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3159,13 +3155,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>439520</v>
+        <v>439589</v>
       </c>
       <c r="R27" t="n">
-        <v>6883088</v>
+        <v>6883504</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3221,10 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132853955</v>
+        <v>132851872</v>
       </c>
       <c r="B28" t="n">
-        <v>80440</v>
+        <v>80489</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3256,13 +3252,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>439099</v>
+        <v>439529</v>
       </c>
       <c r="R28" t="n">
-        <v>6883602</v>
+        <v>6883531</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3318,10 +3314,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132852127</v>
+        <v>132852187</v>
       </c>
       <c r="B29" t="n">
-        <v>79413</v>
+        <v>80489</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3329,21 +3325,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3353,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>439412</v>
+        <v>439386</v>
       </c>
       <c r="R29" t="n">
-        <v>6883600</v>
+        <v>6883624</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3415,10 +3411,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132852187</v>
+        <v>132853541</v>
       </c>
       <c r="B30" t="n">
-        <v>80440</v>
+        <v>80489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3450,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>439386</v>
+        <v>439124</v>
       </c>
       <c r="R30" t="n">
-        <v>6883624</v>
+        <v>6883715</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3512,10 +3508,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132850734</v>
+        <v>132853955</v>
       </c>
       <c r="B31" t="n">
-        <v>79413</v>
+        <v>80489</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3523,21 +3519,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3547,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>439680</v>
+        <v>439099</v>
       </c>
       <c r="R31" t="n">
-        <v>6883392</v>
+        <v>6883602</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3583,11 +3579,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3614,10 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132856616</v>
+        <v>132855166</v>
       </c>
       <c r="B32" t="n">
-        <v>80440</v>
+        <v>80489</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3649,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>439678</v>
+        <v>439162</v>
       </c>
       <c r="R32" t="n">
-        <v>6883172</v>
+        <v>6883543</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3711,10 +3702,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132851377</v>
+        <v>132856616</v>
       </c>
       <c r="B33" t="n">
-        <v>79413</v>
+        <v>80489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3722,21 +3713,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3746,10 +3737,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>439619</v>
+        <v>439678</v>
       </c>
       <c r="R33" t="n">
-        <v>6883455</v>
+        <v>6883172</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3782,11 +3773,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Växer på björk.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3813,10 +3799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132852517</v>
+        <v>132853335</v>
       </c>
       <c r="B34" t="n">
-        <v>79413</v>
+        <v>93271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3824,34 +3810,48 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lillbäcken, Lillbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>439354</v>
+        <v>439146</v>
       </c>
       <c r="R34" t="n">
-        <v>6883624</v>
+        <v>6883811</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -3913,11 +3913,11 @@
         <v>132852715</v>
       </c>
       <c r="B35" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4007,10 +4007,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132851426</v>
+        <v>132848062</v>
       </c>
       <c r="B36" t="n">
-        <v>79413</v>
+        <v>79130</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4042,13 +4042,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>439631</v>
+        <v>439520</v>
       </c>
       <c r="R36" t="n">
-        <v>6883466</v>
+        <v>6883088</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4078,11 +4078,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4109,10 +4104,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132848943</v>
+        <v>132849144</v>
       </c>
       <c r="B37" t="n">
-        <v>80439</v>
+        <v>79130</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,21 +4115,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4144,10 +4139,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439491</v>
+        <v>439508</v>
       </c>
       <c r="R37" t="n">
-        <v>6883182</v>
+        <v>6883212</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4209,7 +4204,7 @@
         <v>132849181</v>
       </c>
       <c r="B38" t="n">
-        <v>79091</v>
+        <v>79130</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4303,10 +4298,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132853499</v>
+        <v>132851342</v>
       </c>
       <c r="B39" t="n">
-        <v>79413</v>
+        <v>79130</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4314,21 +4309,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4338,10 +4333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439076</v>
+        <v>439612</v>
       </c>
       <c r="R39" t="n">
-        <v>6883736</v>
+        <v>6883462</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4400,10 +4395,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132852930</v>
+        <v>132849417</v>
       </c>
       <c r="B40" t="n">
-        <v>79413</v>
+        <v>79992</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4411,21 +4406,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4435,13 +4430,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>439247</v>
+        <v>439558</v>
       </c>
       <c r="R40" t="n">
-        <v>6883824</v>
+        <v>6883256</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4471,11 +4466,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4502,10 +4492,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132853884</v>
+        <v>132852323</v>
       </c>
       <c r="B41" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4513,21 +4503,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4537,10 +4527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>439130</v>
+        <v>439383</v>
       </c>
       <c r="R41" t="n">
-        <v>6883643</v>
+        <v>6883628</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4599,10 +4589,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132851614</v>
+        <v>132854581</v>
       </c>
       <c r="B42" t="n">
-        <v>79413</v>
+        <v>79992</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4610,21 +4600,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4634,10 +4624,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>439614</v>
+        <v>439075</v>
       </c>
       <c r="R42" t="n">
-        <v>6883457</v>
+        <v>6883547</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -4696,10 +4686,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132851872</v>
+        <v>132848943</v>
       </c>
       <c r="B43" t="n">
-        <v>80440</v>
+        <v>80488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4707,21 +4697,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4731,13 +4721,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>439529</v>
+        <v>439491</v>
       </c>
       <c r="R43" t="n">
-        <v>6883531</v>
+        <v>6883182</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4793,10 +4783,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132849316</v>
+        <v>132851598</v>
       </c>
       <c r="B44" t="n">
-        <v>79413</v>
+        <v>80488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4804,21 +4794,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>864</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4828,10 +4818,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>439497</v>
+        <v>439651</v>
       </c>
       <c r="R44" t="n">
-        <v>6883243</v>
+        <v>6883484</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -4864,6 +4854,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4890,32 +4885,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132848015</v>
+        <v>132853019</v>
       </c>
       <c r="B45" t="n">
-        <v>79413</v>
+        <v>80493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4925,10 +4920,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>439534</v>
+        <v>439235</v>
       </c>
       <c r="R45" t="n">
-        <v>6883074</v>
+        <v>6883808</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -4987,32 +4982,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132847930</v>
+        <v>132852000</v>
       </c>
       <c r="B46" t="n">
-        <v>80440</v>
+        <v>57162</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5022,10 +5017,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>439521</v>
+        <v>439419</v>
       </c>
       <c r="R46" t="n">
-        <v>6883085</v>
+        <v>6883604</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5058,6 +5053,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5084,32 +5084,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132852323</v>
+        <v>132852732</v>
       </c>
       <c r="B47" t="n">
-        <v>79953</v>
+        <v>57162</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>439383</v>
+        <v>439310</v>
       </c>
       <c r="R47" t="n">
-        <v>6883628</v>
+        <v>6883738</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5155,6 +5155,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5181,32 +5186,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132849550</v>
+        <v>132852859</v>
       </c>
       <c r="B48" t="n">
-        <v>79413</v>
+        <v>57162</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>864</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5216,10 +5221,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>439556</v>
+        <v>439262</v>
       </c>
       <c r="R48" t="n">
-        <v>6883244</v>
+        <v>6883822</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5252,6 +5257,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5278,32 +5288,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132849417</v>
+        <v>132856227</v>
       </c>
       <c r="B49" t="n">
-        <v>79953</v>
+        <v>98066</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5313,10 +5323,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439558</v>
+        <v>439643</v>
       </c>
       <c r="R49" t="n">
-        <v>6883256</v>
+        <v>6883340</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -5375,32 +5385,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132852000</v>
+        <v>132853397</v>
       </c>
       <c r="B50" t="n">
-        <v>57145</v>
+        <v>79131</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5410,13 +5420,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>439419</v>
+        <v>439117</v>
       </c>
       <c r="R50" t="n">
-        <v>6883604</v>
+        <v>6883809</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5446,11 +5456,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Noterat spillning.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5477,10 +5482,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132849144</v>
+        <v>132854672</v>
       </c>
       <c r="B51" t="n">
-        <v>79091</v>
+        <v>79131</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5488,21 +5493,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5512,10 +5517,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>439508</v>
+        <v>439113</v>
       </c>
       <c r="R51" t="n">
-        <v>6883212</v>
+        <v>6883492</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -5571,6 +5576,103 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132852203</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lillbäcken, Lillbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>439393</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6883615</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60494-2025 artfynd.xlsx
+++ b/artfynd/A 60494-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132849022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132849625</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132849808</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132853884</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132855316</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132848015</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132849316</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132849550</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132850734</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851109</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851231</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851377</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851426</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851614</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851662</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851904</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852127</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2433,6 +2523,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852304</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2530,6 +2625,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852517</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852930</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132853049</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132853499</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,6 +3038,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132854923</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132856307</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3117,6 +3242,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132847930</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3214,6 +3344,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851780</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3311,6 +3446,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851872</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3408,6 +3548,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852187</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3505,6 +3650,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132853541</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3602,6 +3752,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132853955</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3699,6 +3854,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132855166</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3796,6 +3956,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132856616</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3907,6 +4072,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132853335</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4004,6 +4174,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852715</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4101,6 +4276,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132848062</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4198,6 +4378,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132849144</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4295,6 +4480,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132849181</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4392,6 +4582,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851342</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4489,6 +4684,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132849417</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4586,6 +4786,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852323</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4683,6 +4888,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132854581</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4780,6 +4990,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132848943</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4882,6 +5097,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132851598</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4979,6 +5199,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132853019</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5081,6 +5306,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852000</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5183,6 +5413,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852732</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5285,6 +5520,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852859</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5382,6 +5622,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132856227</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5479,6 +5724,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132853397</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5576,6 +5826,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132854672</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5673,8 +5928,66 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852203</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>